--- a/prova_real/trimestre_01_mais_recente/resultado_T1.xlsx
+++ b/prova_real/trimestre_01_mais_recente/resultado_T1.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -595,13 +595,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17.99</v>
+        <v>18.08</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.72</v>
+        <v>68.28</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -624,22 +624,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>9.08</v>
+        <v>10.42</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.3249</v>
+        <v>0.2601</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8102.86</v>
+        <v>9754.290000000001</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>22388.57</v>
+        <v>24040</v>
       </c>
     </row>
     <row r="3">
@@ -655,12 +655,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.98</v>
+        <v>17.12</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>42.63</v>
+        <v>47.23</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.74</v>
+        <v>8.77</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.3769</v>
+        <v>0.3385</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>6090</v>
+        <v>6747.14</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>20375.71</v>
+        <v>21032.86</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +724,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -743,13 +743,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11.15</v>
+        <v>26.95</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.24</v>
+        <v>14.57</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14.49</v>
+        <v>2.98</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>22.27</v>
+        <v>22.78</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-12.9663</v>
+        <v>-3.9674</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2034.29</v>
+        <v>2081.43</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>16320</v>
+        <v>16367.14</v>
       </c>
     </row>
     <row r="5">
@@ -798,17 +798,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.49</v>
+        <v>12.51</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>12.73</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -846,22 +846,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2.95</v>
+        <v>13.18</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>22.48</v>
+        <v>20.18</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-3.688</v>
+        <v>-14.1156</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1351.43</v>
+        <v>1818.57</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>15637.14</v>
+        <v>16104.29</v>
       </c>
     </row>
     <row r="6">
@@ -877,12 +877,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -894,10 +894,10 @@
         <v>56.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.32</v>
+        <v>9.33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.25</v>
+        <v>4.98</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9.75</v>
+        <v>8.82</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>21.16</v>
+        <v>19.39</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-15.0477</v>
+        <v>-15.466</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1178.57</v>
+        <v>711.4299999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>15464.29</v>
+        <v>14997.14</v>
       </c>
     </row>
     <row r="7">
@@ -951,27 +951,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15.31</v>
+        <v>15.16</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.27</v>
+        <v>-3.63</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -980,12 +980,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -994,22 +994,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.43</v>
+        <v>5.19</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.3862</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>38.57</v>
+        <v>-518.5700000000001</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>14324.29</v>
+        <v>13767.14</v>
       </c>
     </row>
     <row r="8">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1042,10 +1042,10 @@
         <v>61.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>191.66</v>
+        <v>189.86</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>-31.65</v>
+        <v>-27.88</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20.55</v>
+        <v>19.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1295.48</v>
+        <v>1238.8</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-7569.5661</v>
+        <v>-8651.1245</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-4521.43</v>
+        <v>-3982.86</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>9764.290000000001</v>
+        <v>10302.86</v>
       </c>
     </row>
     <row r="9">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1116,10 +1116,10 @@
         <v>53.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>7.43</v>
+        <v>8.66</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10.71</v>
+        <v>7.16</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>12.46</v>
+        <v>11.38</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>24.52</v>
+        <v>22.67</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>-18.1631</v>
+        <v>-20.1173</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>0</v>
@@ -1168,17 +1168,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>COCE5</t>
+          <t>CBAV3</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1190,10 +1190,10 @@
         <v>53.2</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5.81</v>
+        <v>33.25</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>8.699999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
         <v>1.11</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>3.63</v>
+        <v>10.46</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.2428</v>
+        <v>-56.5417</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1264,10 +1264,10 @@
         <v>53.2</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>9.970000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-2.46</v>
+        <v>-2.58</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>7.87</v>
+        <v>8.09</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.1226</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>0</v>
@@ -1309,76 +1309,76 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>T-1</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>NGRD3</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>32.06</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>T-1</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>TIMS3</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Pouco Previsível</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>-18.06</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>ALTA</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>ALTA</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N12" s="4" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>-2.3385</v>
-      </c>
-      <c r="P12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="4" t="n">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>QUEDA</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>❌ NÃO</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>⚠️ OBSERVAR</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1390,32 +1390,32 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>CAMB3</t>
+          <t>NGRD3</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>53.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.91</v>
+        <v>2.07</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11.32</v>
+        <v>29.77</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.24</v>
+        <v>4.23</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.53</v>
+        <v>13.12</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1998</v>
+        <v>-3.5768</v>
       </c>
       <c r="P13" s="4" t="n">
         <v>0</v>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1617,27 +1617,27 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>54.8</v>
+        <v>53.2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-4.31</v>
+        <v>-3.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.99</v>
+        <v>-2.04</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.09</v>
+        <v>0.99</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7.28</v>
+        <v>6.55</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.5919</v>
+        <v>-2.0317</v>
       </c>
       <c r="P16" s="4" t="n">
         <v>0</v>
@@ -1686,32 +1686,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>LAND3</t>
+          <t>TUPY3</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54.8</v>
+        <v>58.1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-11.3</v>
+        <v>-12.17</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-3.23</v>
+        <v>-3.82</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1734,13 +1734,13 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>15.48</v>
+        <v>19.34</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-36.1082</v>
+        <v>-6.598</v>
       </c>
       <c r="P17" s="4" t="n">
         <v>0</v>
@@ -1760,17 +1760,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TUPY3</t>
+          <t>SMFT3</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1782,10 +1782,10 @@
         <v>58.1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-13.8</v>
+        <v>-3.29</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-5.4</v>
+        <v>-5.9</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1808,13 +1808,13 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.89</v>
+        <v>3.24</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>21.02</v>
+        <v>17.51</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-7.9204</v>
+        <v>-23.2808</v>
       </c>
       <c r="P18" s="4" t="n">
         <v>0</v>
@@ -1834,36 +1834,36 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SLCE3</t>
+          <t>ODPV3</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>53.2</v>
+        <v>61.3</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.84</v>
+        <v>-4.35</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-5.95</v>
+        <v>-7.12</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>❌ NÃO</t>
+          <t>✅ SIM</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1882,13 +1882,13 @@
         </is>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2</v>
+        <v>2.88</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>11.22</v>
+        <v>20.03</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-5.1564</v>
+        <v>-9.8177</v>
       </c>
       <c r="P19" s="4" t="n">
         <v>0</v>
@@ -1908,17 +1908,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ODPV3</t>
+          <t>SAUD3</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1927,13 +1927,13 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.95</v>
+        <v>-4.35</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-7.38</v>
+        <v>-7.12</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1956,13 +1956,13 @@
         </is>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>21.36</v>
+        <v>20.03</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-11.75</v>
+        <v>-9.8177</v>
       </c>
       <c r="P20" s="4" t="n">
         <v>0</v>
@@ -1982,32 +1982,32 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>SAUD3</t>
+          <t>MYPK3</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>59.7</v>
+        <v>54.8</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.95</v>
+        <v>-17.8</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.38</v>
+        <v>-7.86</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -2030,13 +2030,13 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>3.07</v>
+        <v>0.96</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>21.36</v>
+        <v>10.04</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-11.75</v>
+        <v>-6.4421</v>
       </c>
       <c r="P21" s="4" t="n">
         <v>0</v>
@@ -2056,17 +2056,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SMFT3</t>
+          <t>LAND3</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2078,10 +2078,10 @@
         <v>58.1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.76</v>
+        <v>-9.68</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.95</v>
+        <v>-8.59</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.75</v>
+        <v>1.17</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>20.17</v>
+        <v>13.46</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-27.6763</v>
+        <v>-29.6798</v>
       </c>
       <c r="P22" s="4" t="n">
         <v>0</v>
@@ -2130,32 +2130,32 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>CEAB3</t>
+          <t>TOTS3</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>53.2</v>
+        <v>54.8</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-18.87</v>
+        <v>-1.69</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-10.51</v>
+        <v>-8.91</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -2178,13 +2178,13 @@
         </is>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.1</v>
+        <v>7.74</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>9.09</v>
+        <v>23.15</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-2.2549</v>
+        <v>-20.4488</v>
       </c>
       <c r="P23" s="4" t="n">
         <v>0</v>
@@ -2204,32 +2204,32 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>POMO4</t>
+          <t>CEAB3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>56.5</v>
+        <v>53.2</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-11.1</v>
+        <v>-19.58</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-10.79</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -2252,13 +2252,13 @@
         </is>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.82</v>
+        <v>1.19</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>12.88</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-7.0248</v>
+        <v>-2.7975</v>
       </c>
       <c r="P24" s="4" t="n">
         <v>0</v>
@@ -2278,17 +2278,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SCAR3</t>
+          <t>RAIL3</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2297,13 +2297,13 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>56.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.49</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-11.05</v>
+        <v>-11.02</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>5.05</v>
+        <v>5.34</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.1913</v>
+        <v>-0.2363</v>
       </c>
       <c r="P25" s="4" t="n">
         <v>0</v>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>TOTS3</t>
+          <t>POMO4</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.95</v>
+        <v>-11.02</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-12.16</v>
+        <v>-13.25</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -2400,13 +2400,13 @@
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.23</v>
+        <v>0.78</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>24.58</v>
+        <v>12.27</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-19.9576</v>
+        <v>-6.4825</v>
       </c>
       <c r="P26" s="4" t="n">
         <v>0</v>
@@ -2426,17 +2426,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RAIL3</t>
+          <t>SCAR3</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2445,13 +2445,13 @@
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>67.7</v>
+        <v>58.1</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.64</v>
+        <v>-1.25</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-13.49</v>
+        <v>-13.87</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>5.42</v>
+        <v>4.84</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.6167</v>
+        <v>-0.7114</v>
       </c>
       <c r="P27" s="4" t="n">
         <v>0</v>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MYPK3</t>
+          <t>AERI3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-18.68</v>
+        <v>-22.34</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-14.88</v>
+        <v>-16</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.06</v>
+        <v>0.16</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>11.06</v>
+        <v>6.24</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-6.5872</v>
+        <v>-0.1297</v>
       </c>
       <c r="P28" s="4" t="n">
         <v>0</v>
@@ -2574,32 +2574,32 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>HBOR3</t>
+          <t>MDIA3</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>53.2</v>
+        <v>58.1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-8.74</v>
+        <v>-6.07</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-16.4</v>
+        <v>-17.15</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.22</v>
+        <v>1.63</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.0546</v>
+        <v>-0.539</v>
       </c>
       <c r="P29" s="4" t="n">
         <v>0</v>
@@ -2648,17 +2648,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>MDIA3</t>
+          <t>MBRF3</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2667,13 +2667,13 @@
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>58.1</v>
+        <v>56.5</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-4.94</v>
+        <v>-8.27</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-16.79</v>
+        <v>-18.99</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.74</v>
+        <v>1.29</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8.26</v>
+        <v>6.72</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-1.0808</v>
+        <v>0.0291</v>
       </c>
       <c r="P30" s="4" t="n">
         <v>0</v>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>AERI3</t>
+          <t>RAPT4</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -2744,10 +2744,10 @@
         <v>56.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-21.13</v>
+        <v>-1.42</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-17.92</v>
+        <v>-21.88</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
@@ -2770,13 +2770,13 @@
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.19</v>
+        <v>0.85</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>7.42</v>
+        <v>16.57</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.4267</v>
+        <v>-5.4492</v>
       </c>
       <c r="P31" s="4" t="n">
         <v>0</v>
@@ -2796,32 +2796,32 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SOJA3</t>
+          <t>GMAT3</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Pouco Previsível</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58.1</v>
+        <v>53.2</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-8.57</v>
+        <v>-26.73</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-21.79</v>
+        <v>-22.37</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
@@ -2844,13 +2844,13 @@
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9.289999999999999</v>
+        <v>15.94</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.482</v>
+        <v>-4.5967</v>
       </c>
       <c r="P32" s="4" t="n">
         <v>0</v>
@@ -2870,32 +2870,32 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>RAPT4</t>
+          <t>SOJA3</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>54.8</v>
+        <v>59.7</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2.18</v>
+        <v>-8.93</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-21.99</v>
+        <v>-22.47</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.62</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.4662</v>
+        <v>-0.505</v>
       </c>
       <c r="P33" s="4" t="n">
         <v>0</v>
@@ -2944,32 +2944,32 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>MBRF3</t>
+          <t>HBOR3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
-        <v>58.1</v>
+        <v>54.8</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-9.23</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-22.58</v>
+        <v>-27.35</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.41</v>
+        <v>0.21</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>7.23</v>
+        <v>8.83</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2264</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="P34" s="4" t="n">
         <v>0</v>
@@ -3018,32 +3018,32 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>GMAT3</t>
+          <t>AZZA3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
-        <v>54.8</v>
+        <v>56.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-28.18</v>
+        <v>-11.35</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-25.35</v>
+        <v>-31.87</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
@@ -3066,13 +3066,13 @@
         </is>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.85</v>
+        <v>1.86</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>18.32</v>
+        <v>7.84</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-4.5333</v>
+        <v>0.3542</v>
       </c>
       <c r="P35" s="4" t="n">
         <v>0</v>
@@ -3092,32 +3092,32 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>AZZA3</t>
+          <t>CSAN3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F36" s="4" t="n">
-        <v>54.8</v>
+        <v>61.3</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-12.56</v>
+        <v>-3.34</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-26.21</v>
+        <v>-40.73</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
@@ -3140,13 +3140,13 @@
         </is>
       </c>
       <c r="M36" s="4" t="n">
-        <v>1.95</v>
+        <v>0.66</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>7.9</v>
+        <v>14.5</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.214</v>
+        <v>-1.0603</v>
       </c>
       <c r="P36" s="4" t="n">
         <v>0</v>
@@ -3171,27 +3171,27 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Pouco Previsível</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
-        <v>53.2</v>
+        <v>56.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-18.25</v>
+        <v>-19.13</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>-34.26</v>
+        <v>-40.91</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>11.46</v>
+        <v>10.76</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.3416</v>
+        <v>0.2576</v>
       </c>
       <c r="P37" s="4" t="n">
         <v>0</v>
@@ -3240,17 +3240,17 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>CSAN3</t>
+          <t>ONCO3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3259,13 +3259,13 @@
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>62.9</v>
+        <v>58.1</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>-3.36</v>
+        <v>-44.32</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-39.59</v>
+        <v>-42.92</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
@@ -3288,13 +3288,13 @@
         </is>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.58</v>
+        <v>0.22</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>12.23</v>
+        <v>13.98</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>-0.7196</v>
+        <v>0.2778</v>
       </c>
       <c r="P38" s="4" t="n">
         <v>0</v>
@@ -3314,32 +3314,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>PTBL3</t>
+          <t>LIGT3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>61.3</v>
+        <v>54.8</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-11.96</v>
+        <v>-14.73</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>-41.61</v>
+        <v>-44.07</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.48</v>
+        <v>0.67</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>22.29</v>
+        <v>16.74</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>-0.3967</v>
+        <v>0.1676</v>
       </c>
       <c r="P39" s="4" t="n">
         <v>0</v>
@@ -3388,32 +3388,32 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LIGT3</t>
+          <t>PTBL3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Previsibilidade Moderada</t>
+          <t>Muito Previsível</t>
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-14.89</v>
+        <v>-12.38</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-44.62</v>
+        <v>-45.14</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.65</v>
+        <v>0.52</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>15.22</v>
+        <v>24.41</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.0495</v>
+        <v>-0.5181</v>
       </c>
       <c r="P40" s="4" t="n">
         <v>0</v>
@@ -3462,17 +3462,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ONCO3</t>
+          <t>GFSA3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-53.22</v>
+        <v>-525.4400000000001</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-49.43</v>
+        <v>-47.31</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -3510,13 +3510,13 @@
         </is>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.35</v>
+        <v>3.17</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>20.5</v>
+        <v>234.66</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>-0.2804</v>
+        <v>-140.8493</v>
       </c>
       <c r="P41" s="4" t="n">
         <v>0</v>
@@ -3536,17 +3536,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>GFSA3</t>
+          <t>BHIA3</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3558,10 +3558,10 @@
         <v>59.7</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-491.29</v>
+        <v>-11.25</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-52.32</v>
+        <v>-56.25</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -3584,13 +3584,13 @@
         </is>
       </c>
       <c r="M42" s="4" t="n">
-        <v>3.19</v>
+        <v>0.41</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>228.76</v>
+        <v>25.94</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>-128.6804</v>
+        <v>-0.1495</v>
       </c>
       <c r="P42" s="4" t="n">
         <v>0</v>
@@ -3599,80 +3599,6 @@
         <v>0</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>T-1</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>BHIA3</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>Muito Previsível</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>59.7</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>-9.69</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>-54.52</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>QUEDA</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>✅ SIM</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>❌ NÃO INDICADO</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N43" s="4" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="O43" s="4" t="n">
-        <v>-0.2302</v>
-      </c>
-      <c r="P43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3694,7 +3620,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
@@ -3815,12 +3741,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3829,13 +3755,13 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>58.1</v>
+        <v>59.7</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>17.99</v>
+        <v>18.08</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>56.72</v>
+        <v>68.28</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
@@ -3858,22 +3784,22 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>9.08</v>
+        <v>10.42</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.3249</v>
+        <v>0.2601</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>8102.86</v>
+        <v>9754.290000000001</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>22388.57</v>
+        <v>24040</v>
       </c>
     </row>
     <row r="3">
@@ -3889,12 +3815,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3903,13 +3829,13 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.7</v>
+        <v>61.3</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>16.98</v>
+        <v>17.12</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>42.63</v>
+        <v>47.23</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -3932,22 +3858,22 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>7.74</v>
+        <v>8.77</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.3769</v>
+        <v>0.3385</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>6090</v>
+        <v>6747.14</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>20375.71</v>
+        <v>21032.86</v>
       </c>
     </row>
     <row r="4">
@@ -3958,17 +3884,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PRIO3</t>
+          <t>PINE4</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3977,13 +3903,13 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>58.1</v>
+        <v>61.3</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>11.15</v>
+        <v>26.95</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>14.24</v>
+        <v>14.57</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -4006,22 +3932,22 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14.49</v>
+        <v>2.98</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>22.27</v>
+        <v>22.78</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>-12.9663</v>
+        <v>-3.9674</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2034.29</v>
+        <v>2081.43</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>16320</v>
+        <v>16367.14</v>
       </c>
     </row>
     <row r="5">
@@ -4032,17 +3958,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PINE4</t>
+          <t>PRIO3</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4051,13 +3977,13 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>59.7</v>
+        <v>58.1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.49</v>
+        <v>12.51</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>12.73</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
@@ -4080,22 +4006,22 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2.95</v>
+        <v>13.18</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>22.48</v>
+        <v>20.18</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>-3.688</v>
+        <v>-14.1156</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>1351.43</v>
+        <v>1818.57</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>15637.14</v>
+        <v>16104.29</v>
       </c>
     </row>
     <row r="6">
@@ -4111,12 +4037,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4128,10 +4054,10 @@
         <v>56.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>8.32</v>
+        <v>9.33</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>8.25</v>
+        <v>4.98</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
@@ -4154,22 +4080,22 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>9.75</v>
+        <v>8.82</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>21.16</v>
+        <v>19.39</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>-15.0477</v>
+        <v>-15.466</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>1178.57</v>
+        <v>711.4299999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>15464.29</v>
+        <v>14997.14</v>
       </c>
     </row>
     <row r="7">
@@ -4185,27 +4111,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Muito Previsível</t>
+          <t>Previsibilidade Moderada</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>56.5</v>
+        <v>54.8</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>15.31</v>
+        <v>15.16</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.27</v>
+        <v>-3.63</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
@@ -4214,12 +4140,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>ALTA</t>
+          <t>QUEDA</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>✅ SIM</t>
+          <t>❌ NÃO</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -4228,22 +4154,22 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4.43</v>
+        <v>5.19</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.3862</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>38.57</v>
+        <v>-518.5700000000001</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>14324.29</v>
+        <v>13767.14</v>
       </c>
     </row>
     <row r="8">
@@ -4259,12 +4185,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4276,10 +4202,10 @@
         <v>61.3</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>191.66</v>
+        <v>189.86</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>-31.65</v>
+        <v>-27.88</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -4302,22 +4228,22 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20.55</v>
+        <v>19.44</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1295.48</v>
+        <v>1238.8</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>-7569.5661</v>
+        <v>-8651.1245</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>14285.71</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>-4521.43</v>
+        <v>-3982.86</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>9764.290000000001</v>
+        <v>10302.86</v>
       </c>
     </row>
   </sheetData>
